--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-EX-MedicinalPackageDescription.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-EX-MedicinalPackageDescription.xlsx
@@ -1334,7 +1334,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>105</v>
